--- a/results/components/gene_names/p4s7.xlsx
+++ b/results/components/gene_names/p4s7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>gene1</t>
   </si>
@@ -22,22 +22,34 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Psn</t>
-  </si>
-  <si>
-    <t>Ark</t>
-  </si>
-  <si>
-    <t>Akt1</t>
-  </si>
-  <si>
-    <t>Rack1</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
+    <t>Ef1gamma</t>
+  </si>
+  <si>
+    <t>tin</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>Cka</t>
+  </si>
+  <si>
+    <t>Pk92B</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
   </si>
 </sst>
 </file>
@@ -369,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -404,6 +416,22 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/components/gene_names/p4s7.xlsx
+++ b/results/components/gene_names/p4s7.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>gene1</t>
   </si>
@@ -22,34 +22,40 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>Ef1gamma</t>
-  </si>
-  <si>
-    <t>tin</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>Cka</t>
-  </si>
-  <si>
-    <t>Pk92B</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
+    <t>Syx1A</t>
+  </si>
+  <si>
+    <t>CG32082</t>
+  </si>
+  <si>
+    <t>Sxl</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>ry</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
+    <t>Crk</t>
+  </si>
+  <si>
+    <t>RpL30</t>
+  </si>
+  <si>
+    <t>Nrt</t>
+  </si>
+  <si>
+    <t>Akt1</t>
+  </si>
+  <si>
+    <t>sav</t>
+  </si>
+  <si>
+    <t>crol</t>
   </si>
 </sst>
 </file>
@@ -381,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -432,6 +438,14 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
